--- a/00_Live_Recode_Journal.xlsx
+++ b/00_Live_Recode_Journal.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -607,22 +607,22 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>15875.86</v>
+        <v>38894.06</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-15875.86</v>
+        <v>-38894.06</v>
       </c>
     </row>
     <row r="7">
@@ -665,11 +665,11 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>NA72312</t>
+          <t>NA72114</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>0</v>
@@ -678,11 +678,11 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>NA73513</t>
+          <t>NA72312</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>NA73533</t>
+          <t>NA73513</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
@@ -704,11 +704,11 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>NA73563</t>
+          <t>NA73533</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>0</v>
@@ -717,13 +717,39 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
+          <t>NA73563</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
           <t>NA73564</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B15" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C15" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>NACarried3Jun</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -738,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1522,7 +1548,7 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>72312-&gt;72313 Furniture</t>
+          <t>72114 Reali uniforms</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
@@ -1532,12 +1558,12 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>PK000493</t>
+          <t>PK000012</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>PK000493</t>
+          <t>PK000012</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
@@ -1547,32 +1573,32 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>72312</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>-218.18</v>
+        <v>102.78</v>
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>IKEA TE004431</t>
+          <t>Reali uniform recode fr 20151</t>
         </is>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>Recode 72312 to 72313 F&amp;F</t>
+          <t>PO702344 SI consol Mar-2026</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>EKET storage cabinets not equip</t>
+          <t>72114 net-mvmt (confirm w</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>72312-&gt;72313 Furniture</t>
+          <t>72114 Reali uniforms</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -1582,12 +1608,12 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>PK000493</t>
+          <t>PK000433</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>PK000493</t>
+          <t>PK000433</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -1597,32 +1623,32 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>72313</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G20" s="21" t="n">
-        <v>218.18</v>
+        <v>229.34</v>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>IKEA TE004431</t>
+          <t>Reali uniform recode fr 20151</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>Recode 72312 to 72313 F&amp;F</t>
+          <t>PO702344 SI consol Mar-2026</t>
         </is>
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>EKET storage cabinets not equip</t>
+          <t>72114 net-mvmt (confirm w</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>72312-&gt;72313 Furniture</t>
+          <t>72114 Reali uniforms</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
@@ -1632,12 +1658,12 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000435</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000435</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
@@ -1647,32 +1673,32 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>72312</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G21" s="18" t="n">
-        <v>-2243.09</v>
+        <v>589.63</v>
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>Empire RL196475</t>
+          <t>Reali uniform recode fr 20151</t>
         </is>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
-          <t>Recode 72312 to 72313 F&amp;F</t>
+          <t>PO702344 SI consol Mar-2026</t>
         </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>Chair/desk components &amp; install</t>
+          <t>72114 net-mvmt (confirm w</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>72312-&gt;72313 Furniture</t>
+          <t>72114 Reali uniforms</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
@@ -1682,12 +1708,12 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000003</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000003</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -1697,32 +1723,32 @@
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>72313</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G22" s="21" t="n">
-        <v>2243.09</v>
+        <v>45.29</v>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>Empire RL196475</t>
+          <t>Reali uniform recode fr 20151</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>Recode 72312 to 72313 F&amp;F</t>
+          <t>PO702344 SI consol Mar-2026</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>Chair/desk components &amp; install</t>
+          <t>72114 net-mvmt (confirm w</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>73513 Flair Floral</t>
+          <t>72114 Reali uniforms</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
@@ -1732,12 +1758,12 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000402</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000402</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
@@ -1747,32 +1773,32 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>71111</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>-85</v>
+        <v>92.72</v>
       </c>
       <c r="H23" s="16" t="inlineStr">
         <is>
-          <t>Flair Floral sympathy off 71111</t>
+          <t>Reali uniform recode fr 20151</t>
         </is>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
-          <t>Order1030 ex 85.00 no GST</t>
+          <t>PO702344 SI consol Mar-2026</t>
         </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>To 73513 emp recognition</t>
+          <t>72114 net-mvmt (confirm w</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>73513 Flair Floral</t>
+          <t>72114 Reali uniforms</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
@@ -1797,32 +1823,32 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G24" s="21" t="n">
-        <v>85</v>
+        <v>-1059.76</v>
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>Flair Floral sympathy to 73513</t>
+          <t>Reali uniform recode fr 20151</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>Order1030 ex 85.00 no GST</t>
+          <t>PO702344 SI consol Mar-2026</t>
         </is>
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>From 71111 wages</t>
+          <t>72114 net-mvmt incl 1c rou</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>73533 Travel meal</t>
+          <t>72312-&gt;72313 Furniture</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
@@ -1832,12 +1858,12 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000493</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000493</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
@@ -1847,28 +1873,32 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>73533</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-6.55</v>
+        <v>-218.18</v>
       </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
-          <t>7-Eleven TE005080 meal to 73512</t>
+          <t>IKEA TE004431</t>
         </is>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
-          <t>B refreshment, meal-in-travel</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr"/>
+          <t>Recode 72312 to 72313 F&amp;F</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>EKET storage cabinets not equip</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>73533 Travel meal</t>
+          <t>72312-&gt;72313 Furniture</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
@@ -1878,12 +1908,12 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000493</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000493</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -1893,28 +1923,32 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>72313</t>
         </is>
       </c>
       <c r="G26" s="21" t="n">
-        <v>6.55</v>
+        <v>218.18</v>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>7-Eleven TE005080 meal to 73512</t>
+          <t>IKEA TE004431</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>B refreshment, meal-in-travel</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr"/>
+          <t>Recode 72312 to 72313 F&amp;F</t>
+        </is>
+      </c>
+      <c r="J26" s="19" t="inlineStr">
+        <is>
+          <t>EKET storage cabinets not equip</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>73563 WINC stationery</t>
+          <t>72312-&gt;72313 Furniture</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
@@ -1939,32 +1973,32 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-498.61</v>
+        <v>-2243.09</v>
       </c>
       <c r="H27" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Empire RL196475</t>
         </is>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Recode 72312 to 72313 F&amp;F</t>
         </is>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>Chair/desk components &amp; install</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>73563 WINC stationery</t>
+          <t>72312-&gt;72313 Furniture</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
@@ -1989,32 +2023,32 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>72313</t>
         </is>
       </c>
       <c r="G28" s="21" t="n">
-        <v>498.61</v>
+        <v>2243.09</v>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Empire RL196475</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Recode 72312 to 72313 F&amp;F</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>Chair/desk components &amp; install</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>73563 WINC stationery</t>
+          <t>73513 Flair Floral</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
@@ -2039,32 +2073,32 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>71111</t>
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>-36.62</v>
+        <v>-85</v>
       </c>
       <c r="H29" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Flair Floral sympathy off 71111</t>
         </is>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Order1030 ex 85.00 no GST</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 73513 emp recognition</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>73563 WINC stationery</t>
+          <t>73513 Flair Floral</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -2089,32 +2123,32 @@
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="G30" s="21" t="n">
-        <v>36.62</v>
+        <v>85</v>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Flair Floral sympathy to 73513</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Order1030 ex 85.00 no GST</t>
         </is>
       </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>From 71111 wages</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>73563 WINC stationery</t>
+          <t>73533 Travel meal</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
@@ -2139,32 +2173,28 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>73533</t>
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>-58.58</v>
+        <v>-6.55</v>
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>7-Eleven TE005080 meal to 73512</t>
         </is>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
-        </is>
-      </c>
+          <t>B refreshment, meal-in-travel</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>73563 WINC stationery</t>
+          <t>73533 Travel meal</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -2189,27 +2219,23 @@
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="G32" s="21" t="n">
-        <v>58.58</v>
+        <v>6.55</v>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>7-Eleven TE005080 meal to 73512</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
-        </is>
-      </c>
+          <t>B refreshment, meal-in-travel</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -2243,21 +2269,21 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>-15.56</v>
+        <v>-498.61</v>
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC fly spray frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
-          <t>Mortein insect spray</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>To 72112 Chemical &amp; Pesticide</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -2289,25 +2315,25 @@
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>72112</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G34" s="21" t="n">
-        <v>15.56</v>
+        <v>498.61</v>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC fly spray frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
         <is>
-          <t>Mortein insect spray</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J34" s="19" t="inlineStr">
         <is>
-          <t>To 72112 Chemical &amp; Pesticide</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -2343,21 +2369,21 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>-23.57</v>
+        <v>-36.62</v>
       </c>
       <c r="H35" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC PPE frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
-          <t>First aid vest, nitrile gloves</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>To 72113 Safety Equipment</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -2389,25 +2415,25 @@
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>72113</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G36" s="21" t="n">
-        <v>23.57</v>
+        <v>36.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC PPE frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I36" s="19" t="inlineStr">
         <is>
-          <t>First aid vest, nitrile gloves</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J36" s="19" t="inlineStr">
         <is>
-          <t>To 72113 Safety Equipment</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -2443,21 +2469,21 @@
         </is>
       </c>
       <c r="G37" s="18" t="n">
-        <v>-1305.86</v>
+        <v>-58.58</v>
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC tearoom frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
-          <t>Coffee tea sugar ice (Reason B)</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>To 73512 Hospitality Non-FBT</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -2489,25 +2515,25 @@
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G38" s="21" t="n">
-        <v>1305.86</v>
+        <v>58.58</v>
       </c>
       <c r="H38" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC tearoom frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>Coffee tea sugar ice (Reason B)</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J38" s="19" t="inlineStr">
         <is>
-          <t>To 73512 Hospitality Non-FBT</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -2543,21 +2569,21 @@
         </is>
       </c>
       <c r="G39" s="18" t="n">
-        <v>-1375.15</v>
+        <v>-15.56</v>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC IT items frm 73563</t>
+          <t>Recode WINC fly spray frm 73563</t>
         </is>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
-          <t>Mice, USB cables, kbds, headsets</t>
+          <t>Mortein insect spray</t>
         </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72112 Chemical &amp; Pesticide</t>
         </is>
       </c>
     </row>
@@ -2589,25 +2615,25 @@
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>72112</t>
         </is>
       </c>
       <c r="G40" s="21" t="n">
-        <v>1375.15</v>
+        <v>15.56</v>
       </c>
       <c r="H40" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC IT items frm 73563</t>
+          <t>Recode WINC fly spray frm 73563</t>
         </is>
       </c>
       <c r="I40" s="19" t="inlineStr">
         <is>
-          <t>Mice, USB cables, kbds, headsets</t>
+          <t>Mortein insect spray</t>
         </is>
       </c>
       <c r="J40" s="19" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72112 Chemical &amp; Pesticide</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2650,12 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
@@ -2643,21 +2669,21 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>-98.36</v>
+        <v>-23.57</v>
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Recode WINC PPE frm 73563</t>
         </is>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>First aid vest, nitrile gloves</t>
         </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 72113 Safety Equipment</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2700,12 @@
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
@@ -2689,25 +2715,25 @@
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>72113</t>
         </is>
       </c>
       <c r="G42" s="21" t="n">
-        <v>98.36</v>
+        <v>23.57</v>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Recode WINC PPE frm 73563</t>
         </is>
       </c>
       <c r="I42" s="19" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>First aid vest, nitrile gloves</t>
         </is>
       </c>
       <c r="J42" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 72113 Safety Equipment</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2750,12 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
@@ -2743,21 +2769,21 @@
         </is>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-25.6</v>
+        <v>-1305.86</v>
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Recode WINC tearoom frm 73563</t>
         </is>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Coffee tea sugar ice (Reason B)</t>
         </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 73512 Hospitality Non-FBT</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2800,12 @@
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
@@ -2789,25 +2815,25 @@
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="G44" s="21" t="n">
-        <v>25.6</v>
+        <v>1305.86</v>
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Recode WINC tearoom frm 73563</t>
         </is>
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Coffee tea sugar ice (Reason B)</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 73512 Hospitality Non-FBT</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2850,12 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
@@ -2843,21 +2869,21 @@
         </is>
       </c>
       <c r="G45" s="18" t="n">
-        <v>-36.82</v>
+        <v>-1375.15</v>
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Recode WINC IT items frm 73563</t>
         </is>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Mice, USB cables, kbds, headsets</t>
         </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2900,12 @@
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -2889,25 +2915,25 @@
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="G46" s="21" t="n">
-        <v>36.82</v>
+        <v>1375.15</v>
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC non-stat frm 73563</t>
+          <t>Recode WINC IT items frm 73563</t>
         </is>
       </c>
       <c r="I46" s="19" t="inlineStr">
         <is>
-          <t>Cleaning batt kitchen tools</t>
+          <t>Mice, USB cables, kbds, headsets</t>
         </is>
       </c>
       <c r="J46" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
@@ -2943,21 +2969,21 @@
         </is>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-7.75</v>
+        <v>-98.36</v>
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC PPE frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
-          <t>First aid vest, nitrile gloves</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>To 72113 Safety Equipment</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -2989,25 +3015,25 @@
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
-          <t>72113</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G48" s="21" t="n">
-        <v>7.75</v>
+        <v>98.36</v>
       </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC PPE frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I48" s="19" t="inlineStr">
         <is>
-          <t>First aid vest, nitrile gloves</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J48" s="19" t="inlineStr">
         <is>
-          <t>To 72113 Safety Equipment</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -3043,21 +3069,21 @@
         </is>
       </c>
       <c r="G49" s="18" t="n">
-        <v>-13</v>
+        <v>-25.6</v>
       </c>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC tearoom frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I49" s="16" t="inlineStr">
         <is>
-          <t>Coffee tea sugar ice (Reason B)</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>To 73512 Hospitality Non-FBT</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -3089,25 +3115,25 @@
       </c>
       <c r="F50" s="20" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G50" s="21" t="n">
-        <v>13</v>
+        <v>25.6</v>
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC tearoom frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I50" s="19" t="inlineStr">
         <is>
-          <t>Coffee tea sugar ice (Reason B)</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>To 73512 Hospitality Non-FBT</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -3143,21 +3169,21 @@
         </is>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-357.16</v>
+        <v>-36.82</v>
       </c>
       <c r="H51" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC IT items frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
-          <t>Mice, USB cables, kbds, headsets</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -3189,25 +3215,25 @@
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G52" s="21" t="n">
-        <v>357.16</v>
+        <v>36.82</v>
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC IT items frm 73563</t>
+          <t>Recode WINC non-stat frm 73563</t>
         </is>
       </c>
       <c r="I52" s="19" t="inlineStr">
         <is>
-          <t>Mice, USB cables, kbds, headsets</t>
+          <t>Cleaning batt kitchen tools</t>
         </is>
       </c>
       <c r="J52" s="19" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3250,12 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -3243,21 +3269,21 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>-107.07</v>
+        <v>-7.75</v>
       </c>
       <c r="H53" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Apr non-stat fr 73563</t>
+          <t>Recode WINC PPE frm 73563</t>
         </is>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
-          <t>Cleaning kitchen batteries</t>
+          <t>First aid vest, nitrile gloves</t>
         </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 72113 Safety Equipment</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3300,12 @@
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -3289,25 +3315,25 @@
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>72113</t>
         </is>
       </c>
       <c r="G54" s="21" t="n">
-        <v>107.07</v>
+        <v>7.75</v>
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Apr non-stat fr 73563</t>
+          <t>Recode WINC PPE frm 73563</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>Cleaning kitchen batteries</t>
+          <t>First aid vest, nitrile gloves</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip &amp; Supplies</t>
+          <t>To 72113 Safety Equipment</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3350,12 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
@@ -3343,16 +3369,16 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>-402.07</v>
+        <v>-13</v>
       </c>
       <c r="H55" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Apr tearoom fr 73563</t>
+          <t>Recode WINC tearoom frm 73563</t>
         </is>
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
-          <t>Coffee tea sugar lollies(Rsn B)</t>
+          <t>Coffee tea sugar ice (Reason B)</t>
         </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
@@ -3374,12 +3400,12 @@
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
@@ -3393,16 +3419,16 @@
         </is>
       </c>
       <c r="G56" s="21" t="n">
-        <v>402.07</v>
+        <v>13</v>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Apr tearoom fr 73563</t>
+          <t>Recode WINC tearoom frm 73563</t>
         </is>
       </c>
       <c r="I56" s="19" t="inlineStr">
         <is>
-          <t>Coffee tea sugar lollies(Rsn B)</t>
+          <t>Coffee tea sugar ice (Reason B)</t>
         </is>
       </c>
       <c r="J56" s="19" t="inlineStr">
@@ -3424,12 +3450,12 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
@@ -3443,21 +3469,21 @@
         </is>
       </c>
       <c r="G57" s="18" t="n">
-        <v>-507.51</v>
+        <v>-357.16</v>
       </c>
       <c r="H57" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Apr IT fr 73563</t>
+          <t>Recode WINC IT items frm 73563</t>
         </is>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
-          <t>Headset chargers kbd adapter</t>
+          <t>Mice, USB cables, kbds, headsets</t>
         </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment &amp; Apps</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3500,12 @@
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -3493,21 +3519,21 @@
         </is>
       </c>
       <c r="G58" s="21" t="n">
-        <v>507.51</v>
+        <v>357.16</v>
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Apr IT fr 73563</t>
+          <t>Recode WINC IT items frm 73563</t>
         </is>
       </c>
       <c r="I58" s="19" t="inlineStr">
         <is>
-          <t>Headset chargers kbd adapter</t>
+          <t>Mice, USB cables, kbds, headsets</t>
         </is>
       </c>
       <c r="J58" s="19" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment &amp; Apps</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3550,12 @@
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr">
@@ -3543,7 +3569,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-50.06</v>
+        <v>-107.07</v>
       </c>
       <c r="H59" s="16" t="inlineStr">
         <is>
@@ -3574,12 +3600,12 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
@@ -3593,7 +3619,7 @@
         </is>
       </c>
       <c r="G60" s="21" t="n">
-        <v>50.06</v>
+        <v>107.07</v>
       </c>
       <c r="H60" s="19" t="inlineStr">
         <is>
@@ -3624,12 +3650,12 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
@@ -3643,7 +3669,7 @@
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-19.7</v>
+        <v>-402.07</v>
       </c>
       <c r="H61" s="16" t="inlineStr">
         <is>
@@ -3674,12 +3700,12 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
@@ -3693,7 +3719,7 @@
         </is>
       </c>
       <c r="G62" s="21" t="n">
-        <v>19.7</v>
+        <v>402.07</v>
       </c>
       <c r="H62" s="19" t="inlineStr">
         <is>
@@ -3724,12 +3750,12 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
@@ -3743,7 +3769,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>-101.2</v>
+        <v>-507.51</v>
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
@@ -3774,12 +3800,12 @@
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
@@ -3793,7 +3819,7 @@
         </is>
       </c>
       <c r="G64" s="21" t="n">
-        <v>101.2</v>
+        <v>507.51</v>
       </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
@@ -3824,12 +3850,12 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E65" s="16" t="inlineStr">
@@ -3843,21 +3869,21 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>-260.42</v>
+        <v>-50.06</v>
       </c>
       <c r="H65" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Feb non-stat fr73563</t>
+          <t>Recode WINC Apr non-stat fr 73563</t>
         </is>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
-          <t>Clean kitchen battery storage</t>
+          <t>Cleaning kitchen batteries</t>
         </is>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip&amp;Supplies</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3900,12 @@
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3893,21 +3919,21 @@
         </is>
       </c>
       <c r="G66" s="21" t="n">
-        <v>260.42</v>
+        <v>50.06</v>
       </c>
       <c r="H66" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Feb non-stat fr73563</t>
+          <t>Recode WINC Apr non-stat fr 73563</t>
         </is>
       </c>
       <c r="I66" s="19" t="inlineStr">
         <is>
-          <t>Clean kitchen battery storage</t>
+          <t>Cleaning kitchen batteries</t>
         </is>
       </c>
       <c r="J66" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip&amp;Supplies</t>
+          <t>To 72111 Minor Equip &amp; Supplies</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3950,12 @@
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E67" s="16" t="inlineStr">
@@ -3943,21 +3969,21 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-6.65</v>
+        <v>-19.7</v>
       </c>
       <c r="H67" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Feb disinf fr 73563</t>
+          <t>Recode WINC Apr tearoom fr 73563</t>
         </is>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
-          <t>Glen 20 disinfectant aerosol</t>
+          <t>Coffee tea sugar lollies(Rsn B)</t>
         </is>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>To 72112 Chemical &amp; Pesticide</t>
+          <t>To 73512 Hospitality Non-FBT</t>
         </is>
       </c>
     </row>
@@ -3974,12 +4000,12 @@
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3989,25 +4015,25 @@
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>72112</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="G68" s="21" t="n">
-        <v>6.65</v>
+        <v>19.7</v>
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Feb disinf fr 73563</t>
+          <t>Recode WINC Apr tearoom fr 73563</t>
         </is>
       </c>
       <c r="I68" s="19" t="inlineStr">
         <is>
-          <t>Glen 20 disinfectant aerosol</t>
+          <t>Coffee tea sugar lollies(Rsn B)</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>To 72112 Chemical &amp; Pesticide</t>
+          <t>To 73512 Hospitality Non-FBT</t>
         </is>
       </c>
     </row>
@@ -4024,12 +4050,12 @@
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E69" s="16" t="inlineStr">
@@ -4043,21 +4069,21 @@
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>-23.57</v>
+        <v>-101.2</v>
       </c>
       <c r="H69" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Feb PPE fr 73563</t>
+          <t>Recode WINC Apr IT fr 73563</t>
         </is>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
-          <t>First aid vest</t>
+          <t>Headset chargers kbd adapter</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>To 72113 Safety Equipment</t>
+          <t>To 73564 IT Equipment &amp; Apps</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4100,12 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
@@ -4089,25 +4115,25 @@
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>72113</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="G70" s="21" t="n">
-        <v>23.57</v>
+        <v>101.2</v>
       </c>
       <c r="H70" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Feb PPE fr 73563</t>
+          <t>Recode WINC Apr IT fr 73563</t>
         </is>
       </c>
       <c r="I70" s="19" t="inlineStr">
         <is>
-          <t>First aid vest</t>
+          <t>Headset chargers kbd adapter</t>
         </is>
       </c>
       <c r="J70" s="19" t="inlineStr">
         <is>
-          <t>To 72113 Safety Equipment</t>
+          <t>To 73564 IT Equipment &amp; Apps</t>
         </is>
       </c>
     </row>
@@ -4143,21 +4169,21 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>-353.66</v>
+        <v>-260.42</v>
       </c>
       <c r="H71" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Feb tearoom fr73563</t>
+          <t>Recode WINC Feb non-stat fr73563</t>
         </is>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
-          <t>Coffee Milo ice (Reason B)</t>
+          <t>Clean kitchen battery storage</t>
         </is>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>To 73512 Hospitality Non-FBT</t>
+          <t>To 72111 Minor Equip&amp;Supplies</t>
         </is>
       </c>
     </row>
@@ -4189,25 +4215,25 @@
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G72" s="21" t="n">
-        <v>353.66</v>
+        <v>260.42</v>
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Feb tearoom fr73563</t>
+          <t>Recode WINC Feb non-stat fr73563</t>
         </is>
       </c>
       <c r="I72" s="19" t="inlineStr">
         <is>
-          <t>Coffee Milo ice (Reason B)</t>
+          <t>Clean kitchen battery storage</t>
         </is>
       </c>
       <c r="J72" s="19" t="inlineStr">
         <is>
-          <t>To 73512 Hospitality Non-FBT</t>
+          <t>To 72111 Minor Equip&amp;Supplies</t>
         </is>
       </c>
     </row>
@@ -4243,21 +4269,21 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>-71.56</v>
+        <v>-6.65</v>
       </c>
       <c r="H73" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Feb IT fr 73563</t>
+          <t>Recode WINC Feb disinf fr 73563</t>
         </is>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
-          <t>Apple lightning USB cable</t>
+          <t>Glen 20 disinfectant aerosol</t>
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72112 Chemical &amp; Pesticide</t>
         </is>
       </c>
     </row>
@@ -4289,25 +4315,25 @@
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>72112</t>
         </is>
       </c>
       <c r="G74" s="21" t="n">
-        <v>71.56</v>
+        <v>6.65</v>
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Feb IT fr 73563</t>
+          <t>Recode WINC Feb disinf fr 73563</t>
         </is>
       </c>
       <c r="I74" s="19" t="inlineStr">
         <is>
-          <t>Apple lightning USB cable</t>
+          <t>Glen 20 disinfectant aerosol</t>
         </is>
       </c>
       <c r="J74" s="19" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72112 Chemical &amp; Pesticide</t>
         </is>
       </c>
     </row>
@@ -4324,12 +4350,12 @@
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr">
@@ -4343,21 +4369,21 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-19.83</v>
+        <v>-23.57</v>
       </c>
       <c r="H75" s="16" t="inlineStr">
         <is>
-          <t>Recode WINC Feb non-stat fr73563</t>
+          <t>Recode WINC Feb PPE fr 73563</t>
         </is>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
-          <t>Serviettes plates forks</t>
+          <t>First aid vest</t>
         </is>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip&amp;Supplies</t>
+          <t>To 72113 Safety Equipment</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4400,12 @@
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
@@ -4389,25 +4415,25 @@
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>72113</t>
         </is>
       </c>
       <c r="G76" s="21" t="n">
-        <v>19.83</v>
+        <v>23.57</v>
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>Recode WINC Feb non-stat fr73563</t>
+          <t>Recode WINC Feb PPE fr 73563</t>
         </is>
       </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
-          <t>Serviettes plates forks</t>
+          <t>First aid vest</t>
         </is>
       </c>
       <c r="J76" s="19" t="inlineStr">
         <is>
-          <t>To 72111 Minor Equip&amp;Supplies</t>
+          <t>To 72113 Safety Equipment</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4450,12 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr">
@@ -4443,7 +4469,7 @@
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-51.9</v>
+        <v>-353.66</v>
       </c>
       <c r="H77" s="16" t="inlineStr">
         <is>
@@ -4452,7 +4478,7 @@
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
-          <t>Lollies confectionery (Reason B)</t>
+          <t>Coffee Milo ice (Reason B)</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
@@ -4474,12 +4500,12 @@
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
@@ -4493,7 +4519,7 @@
         </is>
       </c>
       <c r="G78" s="21" t="n">
-        <v>51.9</v>
+        <v>353.66</v>
       </c>
       <c r="H78" s="19" t="inlineStr">
         <is>
@@ -4502,7 +4528,7 @@
       </c>
       <c r="I78" s="19" t="inlineStr">
         <is>
-          <t>Lollies confectionery (Reason B)</t>
+          <t>Coffee Milo ice (Reason B)</t>
         </is>
       </c>
       <c r="J78" s="19" t="inlineStr">
@@ -4524,12 +4550,12 @@
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr">
@@ -4543,7 +4569,7 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>-173.9</v>
+        <v>-71.56</v>
       </c>
       <c r="H79" s="16" t="inlineStr">
         <is>
@@ -4552,7 +4578,7 @@
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
-          <t>Monitor stand keyboard mouse</t>
+          <t>Apple lightning USB cable</t>
         </is>
       </c>
       <c r="J79" s="16" t="inlineStr">
@@ -4574,12 +4600,12 @@
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>PK000086</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
@@ -4593,7 +4619,7 @@
         </is>
       </c>
       <c r="G80" s="21" t="n">
-        <v>173.9</v>
+        <v>71.56</v>
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
@@ -4602,7 +4628,7 @@
       </c>
       <c r="I80" s="19" t="inlineStr">
         <is>
-          <t>Monitor stand keyboard mouse</t>
+          <t>Apple lightning USB cable</t>
         </is>
       </c>
       <c r="J80" s="19" t="inlineStr">
@@ -4624,12 +4650,12 @@
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr">
@@ -4643,21 +4669,21 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>-62.73</v>
+        <v>-19.83</v>
       </c>
       <c r="H81" s="16" t="inlineStr">
         <is>
-          <t>Recode OFW TE005250 fr 73563</t>
+          <t>Recode WINC Feb non-stat fr73563</t>
         </is>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
-          <t>JB 2-in-1 active stylus pen</t>
+          <t>Serviettes plates forks</t>
         </is>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72111 Minor Equip&amp;Supplies</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4700,12 @@
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
@@ -4689,25 +4715,25 @@
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G82" s="21" t="n">
-        <v>62.73</v>
+        <v>19.83</v>
       </c>
       <c r="H82" s="19" t="inlineStr">
         <is>
-          <t>Recode OFW TE005250 fr 73563</t>
+          <t>Recode WINC Feb non-stat fr73563</t>
         </is>
       </c>
       <c r="I82" s="19" t="inlineStr">
         <is>
-          <t>JB 2-in-1 active stylus pen</t>
+          <t>Serviettes plates forks</t>
         </is>
       </c>
       <c r="J82" s="19" t="inlineStr">
         <is>
-          <t>To 73564 IT Equipment</t>
+          <t>To 72111 Minor Equip&amp;Supplies</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4750,12 @@
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr">
@@ -4743,21 +4769,21 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>-290</v>
+        <v>-51.9</v>
       </c>
       <c r="H83" s="16" t="inlineStr">
         <is>
-          <t>Recode OFW TE005250 fr 73563</t>
+          <t>Recode WINC Feb tearoom fr73563</t>
         </is>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
-          <t>Otto+mesh desk risers</t>
+          <t>Lollies confectionery (Reason B)</t>
         </is>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>To 72313 Furniture &amp; Fittings</t>
+          <t>To 73512 Hospitality Non-FBT</t>
         </is>
       </c>
     </row>
@@ -4774,12 +4800,12 @@
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -4789,32 +4815,32 @@
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>72313</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="G84" s="21" t="n">
-        <v>290</v>
+        <v>51.9</v>
       </c>
       <c r="H84" s="19" t="inlineStr">
         <is>
-          <t>Recode OFW TE005250 fr 73563</t>
+          <t>Recode WINC Feb tearoom fr73563</t>
         </is>
       </c>
       <c r="I84" s="19" t="inlineStr">
         <is>
-          <t>Otto+mesh desk risers</t>
+          <t>Lollies confectionery (Reason B)</t>
         </is>
       </c>
       <c r="J84" s="19" t="inlineStr">
         <is>
-          <t>To 72313 Furniture &amp; Fittings</t>
+          <t>To 73512 Hospitality Non-FBT</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>73564 IT Equipment</t>
+          <t>73563 WINC stationery</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
@@ -4824,12 +4850,12 @@
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>PK000087</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D85" s="17" t="inlineStr">
         <is>
-          <t>PK000087</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr">
@@ -4839,32 +4865,32 @@
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>-36.14</v>
+        <v>-173.9</v>
       </c>
       <c r="H85" s="16" t="inlineStr">
         <is>
-          <t>Anthropic Claude reversal</t>
+          <t>Recode WINC Feb IT fr 73563</t>
         </is>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
-          <t>SaaS not 73564 IT equip</t>
+          <t>Monitor stand keyboard mouse</t>
         </is>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>Recode to 73566</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>73564 IT Equipment</t>
+          <t>73563 WINC stationery</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
@@ -4874,12 +4900,12 @@
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>PK000087</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>PK000087</t>
+          <t>PK000086</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
@@ -4889,32 +4915,32 @@
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>73566</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="G86" s="21" t="n">
-        <v>36.14</v>
+        <v>173.9</v>
       </c>
       <c r="H86" s="19" t="inlineStr">
         <is>
-          <t>Anthropic Claude IT SW lic TE005499</t>
+          <t>Recode WINC Feb IT fr 73563</t>
         </is>
       </c>
       <c r="I86" s="19" t="inlineStr">
         <is>
-          <t>Recode from 73564</t>
+          <t>Monitor stand keyboard mouse</t>
         </is>
       </c>
       <c r="J86" s="19" t="inlineStr">
         <is>
-          <t>CN-23167</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>73564 IT Equipment</t>
+          <t>73563 WINC stationery</t>
         </is>
       </c>
       <c r="B87" s="16" t="inlineStr">
@@ -4924,12 +4950,12 @@
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D87" s="17" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
@@ -4939,32 +4965,32 @@
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>-132</v>
+        <v>-62.73</v>
       </c>
       <c r="H87" s="16" t="inlineStr">
         <is>
-          <t>SW licence bundle reversal</t>
+          <t>Recode OFW TE005250 fr 73563</t>
         </is>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
-          <t>SaaS not 73564 IT equip</t>
+          <t>JB 2-in-1 active stylus pen</t>
         </is>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>Recode to 73566</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>73564 IT Equipment</t>
+          <t>73563 WINC stationery</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
@@ -4974,12 +5000,12 @@
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
@@ -4989,32 +5015,32 @@
       </c>
       <c r="F88" s="20" t="inlineStr">
         <is>
-          <t>73566</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="G88" s="21" t="n">
-        <v>132</v>
+        <v>62.73</v>
       </c>
       <c r="H88" s="19" t="inlineStr">
         <is>
-          <t>SW licence bundle IT SW lic INAU004378</t>
+          <t>Recode OFW TE005250 fr 73563</t>
         </is>
       </c>
       <c r="I88" s="19" t="inlineStr">
         <is>
-          <t>Recode from 73564</t>
+          <t>JB 2-in-1 active stylus pen</t>
         </is>
       </c>
       <c r="J88" s="19" t="inlineStr">
         <is>
-          <t>CN-23167</t>
+          <t>To 73564 IT Equipment</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>73564 IT Equipment</t>
+          <t>73563 WINC stationery</t>
         </is>
       </c>
       <c r="B89" s="16" t="inlineStr">
@@ -5024,12 +5050,12 @@
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D89" s="17" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
@@ -5039,32 +5065,32 @@
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>-342</v>
+        <v>-290</v>
       </c>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>SW licence bundle reversal</t>
+          <t>Recode OFW TE005250 fr 73563</t>
         </is>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
-          <t>SaaS not 73564 IT equip</t>
+          <t>Otto+mesh desk risers</t>
         </is>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>Recode to 73566</t>
+          <t>To 72313 Furniture &amp; Fittings</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>73564 IT Equipment</t>
+          <t>73563 WINC stationery</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
@@ -5074,12 +5100,12 @@
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>PK000084</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
@@ -5089,25 +5115,25 @@
       </c>
       <c r="F90" s="20" t="inlineStr">
         <is>
-          <t>73566</t>
+          <t>72313</t>
         </is>
       </c>
       <c r="G90" s="21" t="n">
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="H90" s="19" t="inlineStr">
         <is>
-          <t>SW licence bundle IT SW lic INAU004378</t>
+          <t>Recode OFW TE005250 fr 73563</t>
         </is>
       </c>
       <c r="I90" s="19" t="inlineStr">
         <is>
-          <t>Recode from 73564</t>
+          <t>Otto+mesh desk risers</t>
         </is>
       </c>
       <c r="J90" s="19" t="inlineStr">
         <is>
-          <t>CN-23167</t>
+          <t>To 72313 Furniture &amp; Fittings</t>
         </is>
       </c>
     </row>
@@ -5124,12 +5150,12 @@
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000087</t>
         </is>
       </c>
       <c r="D91" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000087</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
@@ -5143,11 +5169,11 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-372</v>
+        <v>-36.14</v>
       </c>
       <c r="H91" s="16" t="inlineStr">
         <is>
-          <t>Body2 Cam sub reversal</t>
+          <t>Anthropic Claude reversal</t>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
@@ -5174,12 +5200,12 @@
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000087</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000087</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr">
@@ -5193,11 +5219,11 @@
         </is>
       </c>
       <c r="G92" s="21" t="n">
-        <v>372</v>
+        <v>36.14</v>
       </c>
       <c r="H92" s="19" t="inlineStr">
         <is>
-          <t>Body2 Cam sub IT SW lic GJ076194</t>
+          <t>Anthropic Claude IT SW lic TE005499</t>
         </is>
       </c>
       <c r="I92" s="19" t="inlineStr">
@@ -5224,12 +5250,12 @@
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="D93" s="17" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
@@ -5243,11 +5269,11 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>-372</v>
+        <v>-132</v>
       </c>
       <c r="H93" s="16" t="inlineStr">
         <is>
-          <t>Body2 Cam sub reversal</t>
+          <t>SW licence bundle reversal</t>
         </is>
       </c>
       <c r="I93" s="16" t="inlineStr">
@@ -5274,12 +5300,12 @@
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>PK000001</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr">
@@ -5293,11 +5319,11 @@
         </is>
       </c>
       <c r="G94" s="21" t="n">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="H94" s="19" t="inlineStr">
         <is>
-          <t>Body2 Cam sub IT SW lic GJ075813</t>
+          <t>SW licence bundle IT SW lic INAU004378</t>
         </is>
       </c>
       <c r="I94" s="19" t="inlineStr">
@@ -5324,12 +5350,12 @@
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>PK000068</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="D95" s="17" t="inlineStr">
         <is>
-          <t>PK000068</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr">
@@ -5343,11 +5369,11 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>-568.3099999999999</v>
+        <v>-342</v>
       </c>
       <c r="H95" s="16" t="inlineStr">
         <is>
-          <t>Esri ArcGIS reversal</t>
+          <t>SW licence bundle reversal</t>
         </is>
       </c>
       <c r="I95" s="16" t="inlineStr">
@@ -5374,12 +5400,12 @@
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>PK000068</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>PK000068</t>
+          <t>PK000084</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr">
@@ -5393,11 +5419,11 @@
         </is>
       </c>
       <c r="G96" s="21" t="n">
-        <v>568.3099999999999</v>
+        <v>342</v>
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
-          <t>Esri ArcGIS IT SW lic INV000555</t>
+          <t>SW licence bundle IT SW lic INAU004378</t>
         </is>
       </c>
       <c r="I96" s="19" t="inlineStr">
@@ -5414,7 +5440,7 @@
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+          <t>73564 IT Equipment</t>
         </is>
       </c>
       <c r="B97" s="16" t="inlineStr">
@@ -5443,28 +5469,28 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>-30</v>
+        <v>-372</v>
       </c>
       <c r="H97" s="16" t="inlineStr">
         <is>
-          <t>Robertson iPhone off PK000001</t>
+          <t>Body2 Cam sub reversal</t>
         </is>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
-          <t>Trees home 20319 per Spero</t>
+          <t>SaaS not 73564 IT equip</t>
         </is>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>SR219175 PK000001&gt;PK000433</t>
+          <t>Recode to 73566</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="19" t="inlineStr">
         <is>
-          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+          <t>73564 IT Equipment</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
@@ -5474,12 +5500,12 @@
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>PK000433</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>PK000433</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr">
@@ -5489,32 +5515,32 @@
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>73566</t>
         </is>
       </c>
       <c r="G98" s="21" t="n">
-        <v>30</v>
+        <v>372</v>
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
-          <t>Robertson iPhone to PK000433</t>
+          <t>Body2 Cam sub IT SW lic GJ076194</t>
         </is>
       </c>
       <c r="I98" s="19" t="inlineStr">
         <is>
-          <t>Trees Coord Admin home</t>
+          <t>Recode from 73564</t>
         </is>
       </c>
       <c r="J98" s="19" t="inlineStr">
         <is>
-          <t>SR219175 fr PK000001</t>
+          <t>CN-23167</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+          <t>73564 IT Equipment</t>
         </is>
       </c>
       <c r="B99" s="16" t="inlineStr">
@@ -5524,12 +5550,12 @@
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>PK000082</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D99" s="17" t="inlineStr">
         <is>
-          <t>PK000082</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr">
@@ -5543,28 +5569,28 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>-500</v>
+        <v>-372</v>
       </c>
       <c r="H99" s="16" t="inlineStr">
         <is>
-          <t>Dressman Poly off PK000082</t>
+          <t>Body2 Cam sub reversal</t>
         </is>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
-          <t>Branch Mgmt 20001 per Spero</t>
+          <t>SaaS not 73564 IT equip</t>
         </is>
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>SR235810 PK000082&gt;PK000087</t>
+          <t>Recode to 73566</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="19" t="inlineStr">
         <is>
-          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+          <t>73564 IT Equipment</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
@@ -5574,12 +5600,12 @@
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>PK000087</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>PK000087</t>
+          <t>PK000001</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr">
@@ -5589,32 +5615,32 @@
       </c>
       <c r="F100" s="20" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>73566</t>
         </is>
       </c>
       <c r="G100" s="21" t="n">
-        <v>500</v>
+        <v>372</v>
       </c>
       <c r="H100" s="19" t="inlineStr">
         <is>
-          <t>Dressman Poly to PK000087</t>
+          <t>Body2 Cam sub IT SW lic GJ075813</t>
         </is>
       </c>
       <c r="I100" s="19" t="inlineStr">
         <is>
-          <t>Parks Branch Mgmt home</t>
+          <t>Recode from 73564</t>
         </is>
       </c>
       <c r="J100" s="19" t="inlineStr">
         <is>
-          <t>SR235810 fr PK000082</t>
+          <t>CN-23167</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+          <t>73564 IT Equipment</t>
         </is>
       </c>
       <c r="B101" s="16" t="inlineStr">
@@ -5624,12 +5650,12 @@
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>PK000055</t>
+          <t>PK000068</t>
         </is>
       </c>
       <c r="D101" s="17" t="inlineStr">
         <is>
-          <t>PK000055</t>
+          <t>PK000068</t>
         </is>
       </c>
       <c r="E101" s="16" t="inlineStr">
@@ -5643,82 +5669,5138 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>-1929.27</v>
+        <v>-568.3099999999999</v>
       </c>
       <c r="H101" s="16" t="inlineStr">
         <is>
-          <t>Fry iPhone off PK000055</t>
+          <t>Esri ArcGIS reversal</t>
         </is>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
-          <t>Depot 20151 per Spero</t>
+          <t>SaaS not 73564 IT equip</t>
         </is>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>SR0315517 PK000055&gt;PK000001</t>
+          <t>Recode to 73566</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="19" t="inlineStr">
         <is>
+          <t>73564 IT Equipment</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F102" s="20" t="inlineStr">
+        <is>
+          <t>73566</t>
+        </is>
+      </c>
+      <c r="G102" s="21" t="n">
+        <v>568.3099999999999</v>
+      </c>
+      <c r="H102" s="19" t="inlineStr">
+        <is>
+          <t>Esri ArcGIS IT SW lic INV000555</t>
+        </is>
+      </c>
+      <c r="I102" s="19" t="inlineStr">
+        <is>
+          <t>Recode from 73564</t>
+        </is>
+      </c>
+      <c r="J102" s="19" t="inlineStr">
+        <is>
+          <t>CN-23167</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
           <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
         </is>
       </c>
-      <c r="B102" s="19" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="C102" s="20" t="inlineStr">
-        <is>
-          <t>PK000001</t>
-        </is>
-      </c>
-      <c r="D102" s="20" t="inlineStr">
-        <is>
-          <t>PK000001</t>
-        </is>
-      </c>
-      <c r="E102" s="19" t="inlineStr">
-        <is>
-          <t>JOURNAL</t>
-        </is>
-      </c>
-      <c r="F102" s="20" t="inlineStr">
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="inlineStr">
         <is>
           <t>73564</t>
         </is>
       </c>
-      <c r="G102" s="21" t="n">
+      <c r="G103" s="18" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H103" s="16" t="inlineStr">
+        <is>
+          <t>Robertson iPhone off PK000001</t>
+        </is>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>Trees home 20319 per Spero</t>
+        </is>
+      </c>
+      <c r="J103" s="16" t="inlineStr">
+        <is>
+          <t>SR219175 PK000001&gt;PK000433</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="19" t="inlineStr">
+        <is>
+          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+        </is>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>PK000433</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>PK000433</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F104" s="20" t="inlineStr">
+        <is>
+          <t>73564</t>
+        </is>
+      </c>
+      <c r="G104" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H104" s="19" t="inlineStr">
+        <is>
+          <t>Robertson iPhone to PK000433</t>
+        </is>
+      </c>
+      <c r="I104" s="19" t="inlineStr">
+        <is>
+          <t>Trees Coord Admin home</t>
+        </is>
+      </c>
+      <c r="J104" s="19" t="inlineStr">
+        <is>
+          <t>SR219175 fr PK000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C105" s="17" t="inlineStr">
+        <is>
+          <t>PK000082</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>PK000082</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
+          <t>73564</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H105" s="16" t="inlineStr">
+        <is>
+          <t>Dressman Poly off PK000082</t>
+        </is>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>Branch Mgmt 20001 per Spero</t>
+        </is>
+      </c>
+      <c r="J105" s="16" t="inlineStr">
+        <is>
+          <t>SR235810 PK000082&gt;PK000087</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+        </is>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>PK000087</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>PK000087</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F106" s="20" t="inlineStr">
+        <is>
+          <t>73564</t>
+        </is>
+      </c>
+      <c r="G106" s="21" t="n">
+        <v>500</v>
+      </c>
+      <c r="H106" s="19" t="inlineStr">
+        <is>
+          <t>Dressman Poly to PK000087</t>
+        </is>
+      </c>
+      <c r="I106" s="19" t="inlineStr">
+        <is>
+          <t>Parks Branch Mgmt home</t>
+        </is>
+      </c>
+      <c r="J106" s="19" t="inlineStr">
+        <is>
+          <t>SR235810 fr PK000082</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>PK000055</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>PK000055</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>73564</t>
+        </is>
+      </c>
+      <c r="G107" s="18" t="n">
+        <v>-1929.27</v>
+      </c>
+      <c r="H107" s="16" t="inlineStr">
+        <is>
+          <t>Fry iPhone off PK000055</t>
+        </is>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>Depot 20151 per Spero</t>
+        </is>
+      </c>
+      <c r="J107" s="16" t="inlineStr">
+        <is>
+          <t>SR0315517 PK000055&gt;PK000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>73564 IT Equipment - SUB-BATCH B PK ATTRIBUTION NET-MOVES</t>
+        </is>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F108" s="20" t="inlineStr">
+        <is>
+          <t>73564</t>
+        </is>
+      </c>
+      <c r="G108" s="21" t="n">
         <v>1929.27</v>
       </c>
-      <c r="H102" s="19" t="inlineStr">
+      <c r="H108" s="19" t="inlineStr">
         <is>
           <t>Fry iPhone to PK000001</t>
         </is>
       </c>
-      <c r="I102" s="19" t="inlineStr">
+      <c r="I108" s="19" t="inlineStr">
         <is>
           <t>Parks Depot home</t>
         </is>
       </c>
-      <c r="J102" s="19" t="inlineStr">
+      <c r="J108" s="19" t="inlineStr">
         <is>
           <t>SR0315517 fr PK000055</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="F103" s="22" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G109" s="18" t="n">
+        <v>2377.35</v>
+      </c>
+      <c r="H109" s="16" t="inlineStr">
+        <is>
+          <t>J1 recode: Pac Fire PPE</t>
+        </is>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>Ref 188512 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>PPE for fire operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F110" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G110" s="21" t="n">
+        <v>-2377.35</v>
+      </c>
+      <c r="H110" s="19" t="inlineStr">
+        <is>
+          <t>J1 recode: Pac Fire PPE</t>
+        </is>
+      </c>
+      <c r="I110" s="19" t="inlineStr">
+        <is>
+          <t>Ref 188512 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J110" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E111" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="inlineStr">
+        <is>
+          <t>73220</t>
+        </is>
+      </c>
+      <c r="G111" s="18" t="n">
+        <v>1383.29</v>
+      </c>
+      <c r="H111" s="16" t="inlineStr">
+        <is>
+          <t>J2 recode: Altus Traffic</t>
+        </is>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>Ref 410015740 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
+        <is>
+          <t>Traffic control service —</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F112" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G112" s="21" t="n">
+        <v>-1383.29</v>
+      </c>
+      <c r="H112" s="19" t="inlineStr">
+        <is>
+          <t>J2 recode: Altus Traffic</t>
+        </is>
+      </c>
+      <c r="I112" s="19" t="inlineStr">
+        <is>
+          <t>Ref 410015740 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J112" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>73211</t>
+        </is>
+      </c>
+      <c r="G113" s="18" t="n">
+        <v>696.1</v>
+      </c>
+      <c r="H113" s="16" t="inlineStr">
+        <is>
+          <t>J3 recode: Industrial Decontamination</t>
+        </is>
+      </c>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>Ref INV-19260 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J113" s="16" t="inlineStr">
+        <is>
+          <t>PPE decontamination — wild</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E114" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F114" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G114" s="21" t="n">
+        <v>-696.1</v>
+      </c>
+      <c r="H114" s="19" t="inlineStr">
+        <is>
+          <t>J3 recode: Industrial Decontamination</t>
+        </is>
+      </c>
+      <c r="I114" s="19" t="inlineStr">
+        <is>
+          <t>Ref INV-19260 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J114" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="inlineStr">
+        <is>
+          <t>73211</t>
+        </is>
+      </c>
+      <c r="G115" s="18" t="n">
+        <v>560.85</v>
+      </c>
+      <c r="H115" s="16" t="inlineStr">
+        <is>
+          <t>J4 recode: Industrial Decontamination</t>
+        </is>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>Ref INV-18994 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J115" s="16" t="inlineStr">
+        <is>
+          <t>PPE decontamination — wild</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E116" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F116" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G116" s="21" t="n">
+        <v>-560.85</v>
+      </c>
+      <c r="H116" s="19" t="inlineStr">
+        <is>
+          <t>J4 recode: Industrial Decontamination</t>
+        </is>
+      </c>
+      <c r="I116" s="19" t="inlineStr">
+        <is>
+          <t>Ref INV-18994 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J116" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C117" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t>73211</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="n">
+        <v>450.3</v>
+      </c>
+      <c r="H117" s="16" t="inlineStr">
+        <is>
+          <t>J5 recode: Industrial Decontamination</t>
+        </is>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>Ref INV-19437 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J117" s="16" t="inlineStr">
+        <is>
+          <t>PPE decontamination — wild</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F118" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G118" s="21" t="n">
+        <v>-450.3</v>
+      </c>
+      <c r="H118" s="19" t="inlineStr">
+        <is>
+          <t>J5 recode: Industrial Decontamination</t>
+        </is>
+      </c>
+      <c r="I118" s="19" t="inlineStr">
+        <is>
+          <t>Ref INV-19437 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J118" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>PK000075</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>PK000075</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H119" s="16" t="inlineStr">
+        <is>
+          <t>J8 recode: Reptile Awareness Displays</t>
+        </is>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>Ref 003-2026 Svc 20411 (PK000075)</t>
+        </is>
+      </c>
+      <c r="J119" s="16" t="inlineStr">
+        <is>
+          <t>First aid kits — bulk same</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>PK000075</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>PK000075</t>
+        </is>
+      </c>
+      <c r="E120" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F120" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G120" s="21" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H120" s="19" t="inlineStr">
+        <is>
+          <t>J8 recode: Reptile Awareness Displays</t>
+        </is>
+      </c>
+      <c r="I120" s="19" t="inlineStr">
+        <is>
+          <t>Ref 003-2026 Svc 20411 (PK000075)</t>
+        </is>
+      </c>
+      <c r="J120" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="E121" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G121" s="18" t="n">
+        <v>369</v>
+      </c>
+      <c r="H121" s="16" t="inlineStr">
+        <is>
+          <t>J9 recode: Alpha First Aid</t>
+        </is>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8168559 Svc 20662 (PK000496)</t>
+        </is>
+      </c>
+      <c r="J121" s="16" t="inlineStr">
+        <is>
+          <t>First aid kits — bulk same</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="E122" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F122" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G122" s="21" t="n">
+        <v>-369</v>
+      </c>
+      <c r="H122" s="19" t="inlineStr">
+        <is>
+          <t>J9 recode: Alpha First Aid</t>
+        </is>
+      </c>
+      <c r="I122" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8168559 Svc 20662 (PK000496)</t>
+        </is>
+      </c>
+      <c r="J122" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E123" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G123" s="18" t="n">
+        <v>307.35</v>
+      </c>
+      <c r="H123" s="16" t="inlineStr">
+        <is>
+          <t>J10 recode: Pac Fire</t>
+        </is>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>Ref 188738 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J123" s="16" t="inlineStr">
+        <is>
+          <t>Safety boot — individually</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F124" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G124" s="21" t="n">
+        <v>-307.35</v>
+      </c>
+      <c r="H124" s="19" t="inlineStr">
+        <is>
+          <t>J10 recode: Pac Fire</t>
+        </is>
+      </c>
+      <c r="I124" s="19" t="inlineStr">
+        <is>
+          <t>Ref 188738 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J124" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E125" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="n">
+        <v>314.7</v>
+      </c>
+      <c r="H125" s="16" t="inlineStr">
+        <is>
+          <t>J11 recode: Pac Fire</t>
+        </is>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>Ref 183802 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>Safety helmet $299.70 + fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F126" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G126" s="21" t="n">
+        <v>-314.7</v>
+      </c>
+      <c r="H126" s="19" t="inlineStr">
+        <is>
+          <t>J11 recode: Pac Fire</t>
+        </is>
+      </c>
+      <c r="I126" s="19" t="inlineStr">
+        <is>
+          <t>Ref 183802 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J126" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E127" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="inlineStr">
+        <is>
+          <t>72112</t>
+        </is>
+      </c>
+      <c r="G127" s="18" t="n">
+        <v>237.83</v>
+      </c>
+      <c r="H127" s="16" t="inlineStr">
+        <is>
+          <t>J13 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8210/02030503 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>Insecticide + fertiliser</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D128" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F128" s="20" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G128" s="21" t="n">
+        <v>159.43</v>
+      </c>
+      <c r="H128" s="19" t="inlineStr">
+        <is>
+          <t>J13 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I128" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/02030503 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J128" s="19" t="inlineStr">
+        <is>
+          <t>Plants — landscape supplie</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E129" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G129" s="18" t="n">
+        <v>-397.26</v>
+      </c>
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>J13 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8210/02030503 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
+        <is>
+          <t>From 72111 ($0.04 variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B130" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D130" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F130" s="20" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G130" s="21" t="n">
+        <v>324.13</v>
+      </c>
+      <c r="H130" s="19" t="inlineStr">
+        <is>
+          <t>J14 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I130" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8171/01438782 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J130" s="19" t="inlineStr">
+        <is>
+          <t>Ornamental plants — landsc</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E131" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G131" s="18" t="n">
+        <v>-324.13</v>
+      </c>
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>J14 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8171/01438782 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J131" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D132" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F132" s="20" t="inlineStr">
+        <is>
+          <t>72112</t>
+        </is>
+      </c>
+      <c r="G132" s="21" t="n">
+        <v>161.66</v>
+      </c>
+      <c r="H132" s="19" t="inlineStr">
+        <is>
+          <t>J15 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I132" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/01369423 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J132" s="19" t="inlineStr">
+        <is>
+          <t>Chemicals (+$0.01 rounding</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C133" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D133" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E133" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G133" s="18" t="n">
+        <v>147.94</v>
+      </c>
+      <c r="H133" s="16" t="inlineStr">
+        <is>
+          <t>J15 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8210/01369423 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J133" s="16" t="inlineStr">
+        <is>
+          <t>Irrigation/landscape hardw</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D134" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E134" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F134" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G134" s="21" t="n">
+        <v>-309.6</v>
+      </c>
+      <c r="H134" s="19" t="inlineStr">
+        <is>
+          <t>J15 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I134" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/01369423 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J134" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E135" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G135" s="18" t="n">
+        <v>240.23</v>
+      </c>
+      <c r="H135" s="16" t="inlineStr">
+        <is>
+          <t>J16 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8210/01349884 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J135" s="16" t="inlineStr">
+        <is>
+          <t>Landscape supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B136" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D136" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E136" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F136" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G136" s="21" t="n">
+        <v>-240.23</v>
+      </c>
+      <c r="H136" s="19" t="inlineStr">
+        <is>
+          <t>J16 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I136" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/01349884 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J136" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D137" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="H137" s="16" t="inlineStr">
+        <is>
+          <t>J17 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8171/01240231 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J137" s="16" t="inlineStr">
+        <is>
+          <t>Work gloves — PPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B138" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D138" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E138" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F138" s="20" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G138" s="21" t="n">
+        <v>171</v>
+      </c>
+      <c r="H138" s="19" t="inlineStr">
+        <is>
+          <t>J17 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I138" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8171/01240231 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J138" s="19" t="inlineStr">
+        <is>
+          <t>Lopper — small tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D139" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E139" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F139" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G139" s="18" t="n">
+        <v>-226.78</v>
+      </c>
+      <c r="H139" s="16" t="inlineStr">
+        <is>
+          <t>J17 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8171/01240231 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J139" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B140" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D140" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E140" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F140" s="20" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G140" s="21" t="n">
+        <v>203.57</v>
+      </c>
+      <c r="H140" s="19" t="inlineStr">
+        <is>
+          <t>J18 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I140" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8171/01259462 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J140" s="19" t="inlineStr">
+        <is>
+          <t>Artificial plants</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C141" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D141" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G141" s="18" t="n">
+        <v>-203.57</v>
+      </c>
+      <c r="H141" s="16" t="inlineStr">
+        <is>
+          <t>J18 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8171/01259462 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J141" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B142" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D142" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E142" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F142" s="20" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G142" s="21" t="n">
+        <v>210.29</v>
+      </c>
+      <c r="H142" s="19" t="inlineStr">
+        <is>
+          <t>J19 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I142" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8171/01228418 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J142" s="19" t="inlineStr">
+        <is>
+          <t>Plants + chain — landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E143" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="n">
+        <v>-210.29</v>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
+          <t>J19 recode: Bunnings</t>
+        </is>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8171/01228418 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J143" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B144" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E144" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F144" s="20" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G144" s="21" t="n">
+        <v>203.79</v>
+      </c>
+      <c r="H144" s="19" t="inlineStr">
+        <is>
+          <t>J20 recode: Spill Station</t>
+        </is>
+      </c>
+      <c r="I144" s="19" t="inlineStr">
+        <is>
+          <t>Ref 109368 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J144" s="19" t="inlineStr">
+        <is>
+          <t>Spill response — safety eq</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C145" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F145" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G145" s="18" t="n">
+        <v>-203.79</v>
+      </c>
+      <c r="H145" s="16" t="inlineStr">
+        <is>
+          <t>J20 recode: Spill Station</t>
+        </is>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>Ref 109368 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J145" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B146" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D146" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E146" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F146" s="20" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G146" s="21" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="H146" s="19" t="inlineStr">
+        <is>
+          <t>J21 recode: Big Red Truck Fire Rescue</t>
+        </is>
+      </c>
+      <c r="I146" s="19" t="inlineStr">
+        <is>
+          <t>Ref S206895 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J146" s="19" t="inlineStr">
+        <is>
+          <t>Fuel cans — planned burns</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="n">
+        <v>-388.5</v>
+      </c>
+      <c r="H147" s="16" t="inlineStr">
+        <is>
+          <t>J21 recode: Big Red Truck Fire Rescue</t>
+        </is>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>Ref S206895 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="inlineStr">
+        <is>
+          <t>PK000055</t>
+        </is>
+      </c>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>PK000055</t>
+        </is>
+      </c>
+      <c r="E148" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F148" s="20" t="inlineStr">
+        <is>
+          <t>72222</t>
+        </is>
+      </c>
+      <c r="G148" s="21" t="n">
+        <v>335</v>
+      </c>
+      <c r="H148" s="19" t="inlineStr">
+        <is>
+          <t>J22 recode: Tennyson Group</t>
+        </is>
+      </c>
+      <c r="I148" s="19" t="inlineStr">
+        <is>
+          <t>Ref 27577 Svc 20241 (PK000055)</t>
+        </is>
+      </c>
+      <c r="J148" s="19" t="inlineStr">
+        <is>
+          <t>Branded vehicle signage (P</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>PK000055</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="inlineStr">
+        <is>
+          <t>PK000055</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G149" s="18" t="n">
+        <v>-335</v>
+      </c>
+      <c r="H149" s="16" t="inlineStr">
+        <is>
+          <t>J22 recode: Tennyson Group</t>
+        </is>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>Ref 27577 Svc 20241 (PK000055)</t>
+        </is>
+      </c>
+      <c r="J149" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B150" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C150" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D150" s="20" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E150" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F150" s="20" t="inlineStr">
+        <is>
+          <t>72222</t>
+        </is>
+      </c>
+      <c r="G150" s="21" t="n">
+        <v>285</v>
+      </c>
+      <c r="H150" s="19" t="inlineStr">
+        <is>
+          <t>J23 recode: Traffic Control Supplies</t>
+        </is>
+      </c>
+      <c r="I150" s="19" t="inlineStr">
+        <is>
+          <t>Ref 178176 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J150" s="19" t="inlineStr">
+        <is>
+          <t>Branded vehicle signage (p</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>PK000068</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G151" s="18" t="n">
+        <v>-285</v>
+      </c>
+      <c r="H151" s="16" t="inlineStr">
+        <is>
+          <t>J23 recode: Traffic Control Supplies</t>
+        </is>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>Ref 178176 Svc 20401 (PK000068)</t>
+        </is>
+      </c>
+      <c r="J151" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B152" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C152" s="20" t="inlineStr">
+        <is>
+          <t>PK000076</t>
+        </is>
+      </c>
+      <c r="D152" s="20" t="inlineStr">
+        <is>
+          <t>PK000076</t>
+        </is>
+      </c>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F152" s="20" t="inlineStr">
+        <is>
+          <t>72222</t>
+        </is>
+      </c>
+      <c r="G152" s="21" t="n">
+        <v>307</v>
+      </c>
+      <c r="H152" s="19" t="inlineStr">
+        <is>
+          <t>J24 recode: Tennyson Group</t>
+        </is>
+      </c>
+      <c r="I152" s="19" t="inlineStr">
+        <is>
+          <t>Ref 25804 Svc 20412 (PK000076)</t>
+        </is>
+      </c>
+      <c r="J152" s="19" t="inlineStr">
+        <is>
+          <t>Tree Day corflutes — event</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>PK000076</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr">
+        <is>
+          <t>PK000076</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F153" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G153" s="18" t="n">
+        <v>-307</v>
+      </c>
+      <c r="H153" s="16" t="inlineStr">
+        <is>
+          <t>J24 recode: Tennyson Group</t>
+        </is>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>Ref 25804 Svc 20412 (PK000076)</t>
+        </is>
+      </c>
+      <c r="J153" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B154" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C154" s="20" t="inlineStr">
+        <is>
+          <t>PK000445</t>
+        </is>
+      </c>
+      <c r="D154" s="20" t="inlineStr">
+        <is>
+          <t>PK000445</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F154" s="20" t="inlineStr">
+        <is>
+          <t>72248</t>
+        </is>
+      </c>
+      <c r="G154" s="21" t="n">
+        <v>1360</v>
+      </c>
+      <c r="H154" s="19" t="inlineStr">
+        <is>
+          <t>J25 recode: Legacy Monuments</t>
+        </is>
+      </c>
+      <c r="I154" s="19" t="inlineStr">
+        <is>
+          <t>Ref 2591 Svc 20451 (PK000445)</t>
+        </is>
+      </c>
+      <c r="J154" s="19" t="inlineStr">
+        <is>
+          <t>Memorial plaque — cemetery</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>PK000445</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>PK000445</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="n">
+        <v>-1360</v>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>J25 recode: Legacy Monuments</t>
+        </is>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>Ref 2591 Svc 20451 (PK000445)</t>
+        </is>
+      </c>
+      <c r="J155" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="D156" s="20" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="E156" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F156" s="20" t="inlineStr">
+        <is>
+          <t>72249</t>
+        </is>
+      </c>
+      <c r="G156" s="21" t="n">
+        <v>1308.58</v>
+      </c>
+      <c r="H156" s="19" t="inlineStr">
+        <is>
+          <t>J26 recode: Fulton Hogan</t>
+        </is>
+      </c>
+      <c r="I156" s="19" t="inlineStr">
+        <is>
+          <t>Ref 20587563 Svc 20451 (PK000083)</t>
+        </is>
+      </c>
+      <c r="J156" s="19" t="inlineStr">
+        <is>
+          <t>Topsoil — cemeteries groun</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="n">
+        <v>-1308.58</v>
+      </c>
+      <c r="H157" s="16" t="inlineStr">
+        <is>
+          <t>J26 recode: Fulton Hogan</t>
+        </is>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>Ref 20587563 Svc 20451 (PK000083)</t>
+        </is>
+      </c>
+      <c r="J157" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B158" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="E158" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F158" s="20" t="inlineStr">
+        <is>
+          <t>72249</t>
+        </is>
+      </c>
+      <c r="G158" s="21" t="n">
+        <v>841.16</v>
+      </c>
+      <c r="H158" s="19" t="inlineStr">
+        <is>
+          <t>J27 recode: Fulton Hogan</t>
+        </is>
+      </c>
+      <c r="I158" s="19" t="inlineStr">
+        <is>
+          <t>Ref 20672646 Svc 20451 (PK000083)</t>
+        </is>
+      </c>
+      <c r="J158" s="19" t="inlineStr">
+        <is>
+          <t>Topsoil — cemeteries groun</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="D159" s="17" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F159" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G159" s="18" t="n">
+        <v>-841.16</v>
+      </c>
+      <c r="H159" s="16" t="inlineStr">
+        <is>
+          <t>J27 recode: Fulton Hogan</t>
+        </is>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>Ref 20672646 Svc 20451 (PK000083)</t>
+        </is>
+      </c>
+      <c r="J159" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C160" s="20" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="D160" s="20" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F160" s="20" t="inlineStr">
+        <is>
+          <t>72249</t>
+        </is>
+      </c>
+      <c r="G160" s="21" t="n">
+        <v>792.5</v>
+      </c>
+      <c r="H160" s="19" t="inlineStr">
+        <is>
+          <t>J28 recode: Fulton Hogan</t>
+        </is>
+      </c>
+      <c r="I160" s="19" t="inlineStr">
+        <is>
+          <t>Ref 20736903 Svc 20451 (PK000083)</t>
+        </is>
+      </c>
+      <c r="J160" s="19" t="inlineStr">
+        <is>
+          <t>Topsoil — cemeteries groun</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="D161" s="17" t="inlineStr">
+        <is>
+          <t>PK000083</t>
+        </is>
+      </c>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="n">
+        <v>-792.5</v>
+      </c>
+      <c r="H161" s="16" t="inlineStr">
+        <is>
+          <t>J28 recode: Fulton Hogan</t>
+        </is>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>Ref 20736903 Svc 20451 (PK000083)</t>
+        </is>
+      </c>
+      <c r="J161" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B162" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C162" s="20" t="inlineStr">
+        <is>
+          <t>PK000022</t>
+        </is>
+      </c>
+      <c r="D162" s="20" t="inlineStr">
+        <is>
+          <t>PK000022</t>
+        </is>
+      </c>
+      <c r="E162" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F162" s="20" t="inlineStr">
+        <is>
+          <t>72315</t>
+        </is>
+      </c>
+      <c r="G162" s="21" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H162" s="19" t="inlineStr">
+        <is>
+          <t>J29 recode: Petersen Castings</t>
+        </is>
+      </c>
+      <c r="I162" s="19" t="inlineStr">
+        <is>
+          <t>Ref 1215 Svc 20392 (PK000022)</t>
+        </is>
+      </c>
+      <c r="J162" s="19" t="inlineStr">
+        <is>
+          <t>Bin keys — parks assets (b</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C163" s="17" t="inlineStr">
+        <is>
+          <t>PK000022</t>
+        </is>
+      </c>
+      <c r="D163" s="17" t="inlineStr">
+        <is>
+          <t>PK000022</t>
+        </is>
+      </c>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F163" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G163" s="18" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="H163" s="16" t="inlineStr">
+        <is>
+          <t>J29 recode: Petersen Castings</t>
+        </is>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>Ref 1215 Svc 20392 (PK000022)</t>
+        </is>
+      </c>
+      <c r="J163" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C164" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D164" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F164" s="20" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G164" s="21" t="n">
+        <v>913.09</v>
+      </c>
+      <c r="H164" s="19" t="inlineStr">
+        <is>
+          <t>J33 recode: Stihl Shop Jimboomba</t>
+        </is>
+      </c>
+      <c r="I164" s="19" t="inlineStr">
+        <is>
+          <t>Ref 283346 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J164" s="19" t="inlineStr">
+        <is>
+          <t>Stihl chargers — bulk same</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D165" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E165" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F165" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G165" s="18" t="n">
+        <v>-913.09</v>
+      </c>
+      <c r="H165" s="16" t="inlineStr">
+        <is>
+          <t>J33 recode: Stihl Shop Jimboomba</t>
+        </is>
+      </c>
+      <c r="I165" s="16" t="inlineStr">
+        <is>
+          <t>Ref 283346 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J165" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C166" s="20" t="inlineStr">
+        <is>
+          <t>PK000032</t>
+        </is>
+      </c>
+      <c r="D166" s="20" t="inlineStr">
+        <is>
+          <t>PK000032</t>
+        </is>
+      </c>
+      <c r="E166" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F166" s="20" t="inlineStr">
+        <is>
+          <t>72112</t>
+        </is>
+      </c>
+      <c r="G166" s="21" t="n">
+        <v>791</v>
+      </c>
+      <c r="H166" s="19" t="inlineStr">
+        <is>
+          <t>J34 recode: STKISS INITIATOR RB43</t>
+        </is>
+      </c>
+      <c r="I166" s="19" t="inlineStr">
+        <is>
+          <t>Ref 096371 Svc 20381 (PK000032)</t>
+        </is>
+      </c>
+      <c r="J166" s="19" t="inlineStr">
+        <is>
+          <t>INITIATOR 3kg insecticide/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C167" s="17" t="inlineStr">
+        <is>
+          <t>PK000032</t>
+        </is>
+      </c>
+      <c r="D167" s="17" t="inlineStr">
+        <is>
+          <t>PK000032</t>
+        </is>
+      </c>
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F167" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G167" s="18" t="n">
+        <v>-791</v>
+      </c>
+      <c r="H167" s="16" t="inlineStr">
+        <is>
+          <t>J34 recode: STKISS INITIATOR RB43</t>
+        </is>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>Ref 096371 Svc 20381 (PK000032)</t>
+        </is>
+      </c>
+      <c r="J167" s="16" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B168" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C168" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D168" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E168" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F168" s="20" t="inlineStr">
+        <is>
+          <t>72112</t>
+        </is>
+      </c>
+      <c r="G168" s="21" t="n">
+        <v>237.83</v>
+      </c>
+      <c r="H168" s="19" t="inlineStr">
+        <is>
+          <t>J36 recode: Bunnings Underwood</t>
+        </is>
+      </c>
+      <c r="I168" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/00230575 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J168" s="19" t="inlineStr">
+        <is>
+          <t>Chemicals + fertiliser</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D169" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F169" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G169" s="18" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="H169" s="16" t="inlineStr">
+        <is>
+          <t>J36 recode: Bunnings Underwood</t>
+        </is>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8210/00230575 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J169" s="16" t="inlineStr">
+        <is>
+          <t>Safety helmets — PPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B170" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C170" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D170" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E170" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G170" s="21" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="H170" s="19" t="inlineStr">
+        <is>
+          <t>J36 recode: Bunnings Underwood</t>
+        </is>
+      </c>
+      <c r="I170" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/00230575 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J170" s="19" t="inlineStr">
+        <is>
+          <t>Landscape Lock 2L paving a</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D171" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E171" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F171" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G171" s="18" t="n">
+        <v>-303.46</v>
+      </c>
+      <c r="H171" s="16" t="inlineStr">
+        <is>
+          <t>J36 recode: Bunnings Underwood</t>
+        </is>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8210/00230575 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J171" s="16" t="inlineStr">
+        <is>
+          <t>From 72111 (watering can $</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B172" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C172" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D172" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E172" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F172" s="20" t="inlineStr">
+        <is>
+          <t>72112</t>
+        </is>
+      </c>
+      <c r="G172" s="21" t="n">
+        <v>185.05</v>
+      </c>
+      <c r="H172" s="19" t="inlineStr">
+        <is>
+          <t>J37 recode: Bunnings Underwood</t>
+        </is>
+      </c>
+      <c r="I172" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/02056322 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J172" s="19" t="inlineStr">
+        <is>
+          <t>Powerfeed 10L x2 (bulk) +</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C173" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D173" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E173" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F173" s="17" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="G173" s="18" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="H173" s="16" t="inlineStr">
+        <is>
+          <t>J37 recode: Bunnings Underwood</t>
+        </is>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>Ref 8210/02056322 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J173" s="16" t="inlineStr">
+        <is>
+          <t>Mixed plants (marigold, le</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B174" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D174" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E174" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G174" s="21" t="n">
+        <v>-264.75</v>
+      </c>
+      <c r="H174" s="19" t="inlineStr">
+        <is>
+          <t>J37 recode: Bunnings Underwood</t>
+        </is>
+      </c>
+      <c r="I174" s="19" t="inlineStr">
+        <is>
+          <t>Ref 8210/02056322 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J174" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="D175" s="17" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="E175" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F175" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="n">
+        <v>418.22</v>
+      </c>
+      <c r="H175" s="16" t="inlineStr">
+        <is>
+          <t>J35a recode: STKISS LITTER PIC JF51</t>
+        </is>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>Ref 092580 Svc 20662 (PK000496)</t>
+        </is>
+      </c>
+      <c r="J175" s="16" t="inlineStr">
+        <is>
+          <t>Litter pickers — field ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B176" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C176" s="20" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="D176" s="20" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="E176" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F176" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G176" s="21" t="n">
+        <v>-418.22</v>
+      </c>
+      <c r="H176" s="19" t="inlineStr">
+        <is>
+          <t>J35a recode: STKISS LITTER PIC JF51</t>
+        </is>
+      </c>
+      <c r="I176" s="19" t="inlineStr">
+        <is>
+          <t>Ref 092580 Svc 20662 (PK000496)</t>
+        </is>
+      </c>
+      <c r="J176" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C177" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D177" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E177" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F177" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G177" s="18" t="n">
+        <v>331.18</v>
+      </c>
+      <c r="H177" s="16" t="inlineStr">
+        <is>
+          <t>J35b recode: STKISS LCC AWARE RB22</t>
+        </is>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>Ref 093813 Svc 20151 (PK000001)</t>
+        </is>
+      </c>
+      <c r="J177" s="16" t="inlineStr">
+        <is>
+          <t>LCC Aware tape — site safe</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B178" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C178" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D178" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E178" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G178" s="21" t="n">
+        <v>-331.18</v>
+      </c>
+      <c r="H178" s="19" t="inlineStr">
+        <is>
+          <t>J35b recode: STKISS LCC AWARE RB22</t>
+        </is>
+      </c>
+      <c r="I178" s="19" t="inlineStr">
+        <is>
+          <t>Ref 093813 Svc 20151 (PK000001)</t>
+        </is>
+      </c>
+      <c r="J178" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B179" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C179" s="17" t="inlineStr">
+        <is>
+          <t>PK000493</t>
+        </is>
+      </c>
+      <c r="D179" s="17" t="inlineStr">
+        <is>
+          <t>PK000493</t>
+        </is>
+      </c>
+      <c r="E179" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F179" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G179" s="18" t="n">
+        <v>562.79</v>
+      </c>
+      <c r="H179" s="16" t="inlineStr">
+        <is>
+          <t>J35c recode: STKISS SITE BARRI XI11</t>
+        </is>
+      </c>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>Ref 095340 Svc 20392 (PK000493)</t>
+        </is>
+      </c>
+      <c r="J179" s="16" t="inlineStr">
+        <is>
+          <t>Site barrier mesh — bulk s</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C180" s="20" t="inlineStr">
+        <is>
+          <t>PK000493</t>
+        </is>
+      </c>
+      <c r="D180" s="20" t="inlineStr">
+        <is>
+          <t>PK000493</t>
+        </is>
+      </c>
+      <c r="E180" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F180" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G180" s="21" t="n">
+        <v>-562.79</v>
+      </c>
+      <c r="H180" s="19" t="inlineStr">
+        <is>
+          <t>J35c recode: STKISS SITE BARRI XI11</t>
+        </is>
+      </c>
+      <c r="I180" s="19" t="inlineStr">
+        <is>
+          <t>Ref 095340 Svc 20392 (PK000493)</t>
+        </is>
+      </c>
+      <c r="J180" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="D181" s="17" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="E181" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F181" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G181" s="18" t="n">
+        <v>227.09</v>
+      </c>
+      <c r="H181" s="16" t="inlineStr">
+        <is>
+          <t>J35d recode: STKISS TRIMMER CO RC42</t>
+        </is>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>Ref 095736 Svc 20440 (PK000003)</t>
+        </is>
+      </c>
+      <c r="J181" s="16" t="inlineStr">
+        <is>
+          <t>Trimmer cord — power tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B182" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C182" s="20" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="D182" s="20" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="E182" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F182" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G182" s="21" t="n">
+        <v>-227.09</v>
+      </c>
+      <c r="H182" s="19" t="inlineStr">
+        <is>
+          <t>J35d recode: STKISS TRIMMER CO RC42</t>
+        </is>
+      </c>
+      <c r="I182" s="19" t="inlineStr">
+        <is>
+          <t>Ref 095736 Svc 20440 (PK000003)</t>
+        </is>
+      </c>
+      <c r="J182" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B183" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C183" s="17" t="inlineStr">
+        <is>
+          <t>PK000084</t>
+        </is>
+      </c>
+      <c r="D183" s="17" t="inlineStr">
+        <is>
+          <t>PK000084</t>
+        </is>
+      </c>
+      <c r="E183" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F183" s="17" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+      <c r="G183" s="18" t="n">
+        <v>343.46</v>
+      </c>
+      <c r="H183" s="16" t="inlineStr">
+        <is>
+          <t>J35e recode: STKISS ELECTROLYT RE21</t>
+        </is>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>Ref 095893 Svc 20301 (PK000084)</t>
+        </is>
+      </c>
+      <c r="J183" s="16" t="inlineStr">
+        <is>
+          <t>Electrolyte drink — crew h</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C184" s="20" t="inlineStr">
+        <is>
+          <t>PK000084</t>
+        </is>
+      </c>
+      <c r="D184" s="20" t="inlineStr">
+        <is>
+          <t>PK000084</t>
+        </is>
+      </c>
+      <c r="E184" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F184" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G184" s="21" t="n">
+        <v>-343.46</v>
+      </c>
+      <c r="H184" s="19" t="inlineStr">
+        <is>
+          <t>J35e recode: STKISS ELECTROLYT RE21</t>
+        </is>
+      </c>
+      <c r="I184" s="19" t="inlineStr">
+        <is>
+          <t>Ref 095893 Svc 20301 (PK000084)</t>
+        </is>
+      </c>
+      <c r="J184" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B185" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C185" s="17" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="D185" s="17" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="E185" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F185" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G185" s="18" t="n">
+        <v>285.49</v>
+      </c>
+      <c r="H185" s="16" t="inlineStr">
+        <is>
+          <t>J35f recode: STKISS LITTER PIC LF21</t>
+        </is>
+      </c>
+      <c r="I185" s="16" t="inlineStr">
+        <is>
+          <t>Ref 096300 Svc 20662 (PK000496)</t>
+        </is>
+      </c>
+      <c r="J185" s="16" t="inlineStr">
+        <is>
+          <t>Litter pickers — field ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B186" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C186" s="20" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="D186" s="20" t="inlineStr">
+        <is>
+          <t>PK000496</t>
+        </is>
+      </c>
+      <c r="E186" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F186" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G186" s="21" t="n">
+        <v>-285.49</v>
+      </c>
+      <c r="H186" s="19" t="inlineStr">
+        <is>
+          <t>J35f recode: STKISS LITTER PIC LF21</t>
+        </is>
+      </c>
+      <c r="I186" s="19" t="inlineStr">
+        <is>
+          <t>Ref 096300 Svc 20662 (PK000496)</t>
+        </is>
+      </c>
+      <c r="J186" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B187" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D187" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E187" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F187" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G187" s="18" t="n">
+        <v>286.06</v>
+      </c>
+      <c r="H187" s="16" t="inlineStr">
+        <is>
+          <t>J35g recode: STKISS LITTER PIC LF21</t>
+        </is>
+      </c>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>Ref 096601 Svc 20151 (PK000001)</t>
+        </is>
+      </c>
+      <c r="J187" s="16" t="inlineStr">
+        <is>
+          <t>Litter pickers — field ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C188" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D188" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E188" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F188" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G188" s="21" t="n">
+        <v>-286.06</v>
+      </c>
+      <c r="H188" s="19" t="inlineStr">
+        <is>
+          <t>J35g recode: STKISS LITTER PIC LF21</t>
+        </is>
+      </c>
+      <c r="I188" s="19" t="inlineStr">
+        <is>
+          <t>Ref 096601 Svc 20151 (PK000001)</t>
+        </is>
+      </c>
+      <c r="J188" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B189" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C189" s="17" t="inlineStr">
+        <is>
+          <t>PK000435</t>
+        </is>
+      </c>
+      <c r="D189" s="17" t="inlineStr">
+        <is>
+          <t>PK000435</t>
+        </is>
+      </c>
+      <c r="E189" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F189" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G189" s="18" t="n">
+        <v>241.43</v>
+      </c>
+      <c r="H189" s="16" t="inlineStr">
+        <is>
+          <t>J35h recode: STKISS TRAFFIC CO XF11</t>
+        </is>
+      </c>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>Ref 096664 Svc 20362 (PK000435)</t>
+        </is>
+      </c>
+      <c r="J189" s="16" t="inlineStr">
+        <is>
+          <t>Traffic cones — bulk same-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B190" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C190" s="20" t="inlineStr">
+        <is>
+          <t>PK000435</t>
+        </is>
+      </c>
+      <c r="D190" s="20" t="inlineStr">
+        <is>
+          <t>PK000435</t>
+        </is>
+      </c>
+      <c r="E190" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F190" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G190" s="21" t="n">
+        <v>-241.43</v>
+      </c>
+      <c r="H190" s="19" t="inlineStr">
+        <is>
+          <t>J35h recode: STKISS TRAFFIC CO XF11</t>
+        </is>
+      </c>
+      <c r="I190" s="19" t="inlineStr">
+        <is>
+          <t>Ref 096664 Svc 20362 (PK000435)</t>
+        </is>
+      </c>
+      <c r="J190" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B191" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C191" s="17" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="D191" s="17" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="E191" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F191" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G191" s="18" t="n">
+        <v>229.11</v>
+      </c>
+      <c r="H191" s="16" t="inlineStr">
+        <is>
+          <t>J35i recode: STKISS TRIMMER CO RC42</t>
+        </is>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>Ref 097341 Svc 20440 (PK000003)</t>
+        </is>
+      </c>
+      <c r="J191" s="16" t="inlineStr">
+        <is>
+          <t>Trimmer cord — power tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B192" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C192" s="20" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="D192" s="20" t="inlineStr">
+        <is>
+          <t>PK000003</t>
+        </is>
+      </c>
+      <c r="E192" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F192" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G192" s="21" t="n">
+        <v>-229.11</v>
+      </c>
+      <c r="H192" s="19" t="inlineStr">
+        <is>
+          <t>J35i recode: STKISS TRIMMER CO RC42</t>
+        </is>
+      </c>
+      <c r="I192" s="19" t="inlineStr">
+        <is>
+          <t>Ref 097341 Svc 20440 (PK000003)</t>
+        </is>
+      </c>
+      <c r="J192" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B193" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C193" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D193" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E193" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F193" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G193" s="18" t="n">
+        <v>229.11</v>
+      </c>
+      <c r="H193" s="16" t="inlineStr">
+        <is>
+          <t>J35j recode: STKISS TRIMMER CO RC42</t>
+        </is>
+      </c>
+      <c r="I193" s="16" t="inlineStr">
+        <is>
+          <t>Ref 097673 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J193" s="16" t="inlineStr">
+        <is>
+          <t>Trimmer cord — power tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B194" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C194" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D194" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E194" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F194" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G194" s="21" t="n">
+        <v>-229.11</v>
+      </c>
+      <c r="H194" s="19" t="inlineStr">
+        <is>
+          <t>J35j recode: STKISS TRIMMER CO RC42</t>
+        </is>
+      </c>
+      <c r="I194" s="19" t="inlineStr">
+        <is>
+          <t>Ref 097673 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J194" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B195" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C195" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D195" s="17" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F195" s="17" t="inlineStr">
+        <is>
+          <t>72311</t>
+        </is>
+      </c>
+      <c r="G195" s="18" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="H195" s="16" t="inlineStr">
+        <is>
+          <t>J35k recode: STKISS STAR PICKE WD26</t>
+        </is>
+      </c>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>Ref 097868 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J195" s="16" t="inlineStr">
+        <is>
+          <t>Star pickets — bulk same-i</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B196" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C196" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="D196" s="20" t="inlineStr">
+        <is>
+          <t>PK000012</t>
+        </is>
+      </c>
+      <c r="E196" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F196" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G196" s="21" t="n">
+        <v>-334.16</v>
+      </c>
+      <c r="H196" s="19" t="inlineStr">
+        <is>
+          <t>J35k recode: STKISS STAR PICKE WD26</t>
+        </is>
+      </c>
+      <c r="I196" s="19" t="inlineStr">
+        <is>
+          <t>Ref 097868 Svc 20181 (PK000012)</t>
+        </is>
+      </c>
+      <c r="J196" s="19" t="inlineStr">
+        <is>
+          <t>From 72111</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B197" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C197" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D197" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E197" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F197" s="17" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G197" s="18" t="n">
+        <v>-473.64</v>
+      </c>
+      <c r="H197" s="16" t="inlineStr">
+        <is>
+          <t>13-Jan-2026</t>
+        </is>
+      </c>
+      <c r="I197" s="16" t="inlineStr">
+        <is>
+          <t>OFFICEWORKS</t>
+        </is>
+      </c>
+      <c r="J197" s="16" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B198" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C198" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D198" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E198" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F198" s="20" t="inlineStr">
+        <is>
+          <t>73563</t>
+        </is>
+      </c>
+      <c r="G198" s="21" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="H198" s="19" t="inlineStr">
+        <is>
+          <t>3× 2026 Collins A5 Diary</t>
+        </is>
+      </c>
+      <c r="I198" s="19" t="inlineStr">
+        <is>
+          <t>OFFICEWORKS</t>
+        </is>
+      </c>
+      <c r="J198" s="19" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B199" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D199" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F199" s="17" t="inlineStr">
+        <is>
+          <t>72313</t>
+        </is>
+      </c>
+      <c r="G199" s="18" t="n">
+        <v>398.18</v>
+      </c>
+      <c r="H199" s="16" t="inlineStr">
+        <is>
+          <t>20× Otto Acrylic Desk Riser Large + 2×</t>
+        </is>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>OFFICEWORKS</t>
+        </is>
+      </c>
+      <c r="J199" s="16" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B200" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C200" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D200" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E200" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F200" s="20" t="inlineStr">
+        <is>
+          <t>73564</t>
+        </is>
+      </c>
+      <c r="G200" s="21" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="H200" s="19" t="inlineStr">
+        <is>
+          <t>1× USB-C / SD Card Reader Adapter</t>
+        </is>
+      </c>
+      <c r="I200" s="19" t="inlineStr">
+        <is>
+          <t>OFFICEWORKS</t>
+        </is>
+      </c>
+      <c r="J200" s="19" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B201" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C201" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D201" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F201" s="17" t="inlineStr">
+        <is>
+          <t>72313</t>
+        </is>
+      </c>
+      <c r="G201" s="18" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="H201" s="16" t="inlineStr">
+        <is>
+          <t>3× Otto Acrylic Desk Riser Large</t>
+        </is>
+      </c>
+      <c r="I201" s="16" t="inlineStr">
+        <is>
+          <t>OFFICEWORKS</t>
+        </is>
+      </c>
+      <c r="J201" s="16" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B202" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C202" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D202" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E202" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F202" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G202" s="21" t="n">
+        <v>-54.52</v>
+      </c>
+      <c r="H202" s="19" t="inlineStr">
+        <is>
+          <t>TE004824</t>
+        </is>
+      </c>
+      <c r="I202" s="19" t="inlineStr"/>
+      <c r="J202" s="19" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="16" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B203" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D203" s="17" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E203" s="16" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F203" s="17" t="inlineStr">
+        <is>
+          <t>72248</t>
+        </is>
+      </c>
+      <c r="G203" s="18" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="H203" s="16" t="inlineStr">
+        <is>
+          <t>TE004478</t>
+        </is>
+      </c>
+      <c r="I203" s="16" t="inlineStr"/>
+      <c r="J203" s="16" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="19" t="inlineStr">
+        <is>
+          <t>Carried 3-Jun (Doc46+PCard)</t>
+        </is>
+      </c>
+      <c r="B204" s="19" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C204" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="D204" s="20" t="inlineStr">
+        <is>
+          <t>PK000001</t>
+        </is>
+      </c>
+      <c r="E204" s="19" t="inlineStr">
+        <is>
+          <t>JOURNAL</t>
+        </is>
+      </c>
+      <c r="F204" s="20" t="inlineStr">
+        <is>
+          <t>72111</t>
+        </is>
+      </c>
+      <c r="G204" s="21" t="n">
+        <v>-27.55</v>
+      </c>
+      <c r="H204" s="19" t="inlineStr">
+        <is>
+          <t>TE004478</t>
+        </is>
+      </c>
+      <c r="I204" s="19" t="inlineStr"/>
+      <c r="J204" s="19" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="F205" s="22" t="inlineStr">
         <is>
           <t>BATCH NET</t>
         </is>
       </c>
-      <c r="G103" s="23">
-        <f>SUM(G5:G102)</f>
+      <c r="G205" s="23">
+        <f>SUM(G5:G204)</f>
         <v/>
       </c>
     </row>
@@ -5733,7 +10815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5786,7 +10868,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>-598.88</v>
+        <v>-22557.32</v>
       </c>
     </row>
     <row r="7">
@@ -5796,7 +10878,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>22.21</v>
+        <v>1635.58</v>
       </c>
     </row>
     <row r="8">
@@ -5806,106 +10888,186 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1813.01</v>
+        <v>6336.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>72312</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>-2461.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>72313</t>
+          <t>72222</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>2751.27</v>
+        <v>927</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>72315</t>
+          <t>72231</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>439.68</v>
+        <v>1409.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>2152.74</v>
+        <v>1387.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>72249</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>85</v>
+        <v>2942.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>73533</t>
+          <t>72311</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>-6.55</v>
+        <v>4286.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>-6313.42</v>
+        <v>-2461.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>72313</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>826.76</v>
+        <v>3203.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
+          <t>72315</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1689.68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>73211</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1707.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>73220</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1383.29</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>73512</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>2152.74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>73513</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>73533</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>-6.55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>73563</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>-6269.78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>73564</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>858.58</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
           <t>73566</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B25" s="10" t="n">
         <v>1822.45</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>GRAND NET</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B26" s="23" t="n">
         <v>0</v>
       </c>
     </row>
